--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -7623,10 +7623,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119558967</v>
+        <v>119558957</v>
       </c>
       <c r="B70" t="n">
-        <v>90509</v>
+        <v>87406</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7639,21 +7639,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>112</v>
+        <v>4412</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>763297</v>
+        <v>763026</v>
       </c>
       <c r="R70" t="n">
-        <v>7306876</v>
+        <v>7306885</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7729,10 +7729,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119558957</v>
+        <v>119558967</v>
       </c>
       <c r="B71" t="n">
-        <v>87406</v>
+        <v>90509</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7745,21 +7745,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4412</v>
+        <v>112</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>763026</v>
+        <v>763297</v>
       </c>
       <c r="R71" t="n">
-        <v>7306885</v>
+        <v>7306876</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9107,10 +9107,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119557856</v>
+        <v>119559028</v>
       </c>
       <c r="B84" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9119,25 +9119,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>762996</v>
+        <v>762957</v>
       </c>
       <c r="R84" t="n">
-        <v>7306937</v>
+        <v>7306896</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9197,12 +9197,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9213,10 +9213,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119559028</v>
+        <v>119557856</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9225,25 +9225,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>762957</v>
+        <v>762996</v>
       </c>
       <c r="R85" t="n">
-        <v>7306896</v>
+        <v>7306937</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9303,12 +9303,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -7835,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119557869</v>
+        <v>119557854</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7847,25 +7847,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>763366</v>
+        <v>762984</v>
       </c>
       <c r="R72" t="n">
-        <v>7306697</v>
+        <v>7306966</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7941,10 +7941,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119557854</v>
+        <v>119557869</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7953,25 +7953,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>762984</v>
+        <v>763366</v>
       </c>
       <c r="R73" t="n">
-        <v>7306966</v>
+        <v>7306697</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9107,10 +9107,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119559028</v>
+        <v>119557856</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9119,25 +9119,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>762957</v>
+        <v>762996</v>
       </c>
       <c r="R84" t="n">
-        <v>7306896</v>
+        <v>7306937</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9197,12 +9197,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9213,10 +9213,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119557856</v>
+        <v>119559028</v>
       </c>
       <c r="B85" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9225,25 +9225,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>762996</v>
+        <v>762957</v>
       </c>
       <c r="R85" t="n">
-        <v>7306937</v>
+        <v>7306896</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9303,12 +9303,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -7305,10 +7305,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119559029</v>
+        <v>119559016</v>
       </c>
       <c r="B67" t="n">
-        <v>91128</v>
+        <v>97907</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7321,21 +7321,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>763197</v>
+        <v>763454</v>
       </c>
       <c r="R67" t="n">
-        <v>7306894</v>
+        <v>7306636</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7411,10 +7411,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119559023</v>
+        <v>119558862</v>
       </c>
       <c r="B68" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7423,25 +7423,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>762960</v>
+        <v>763006</v>
       </c>
       <c r="R68" t="n">
-        <v>7306894</v>
+        <v>7306911</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7501,12 +7501,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7517,10 +7517,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119559018</v>
+        <v>119557792</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7529,25 +7529,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7557,10 +7557,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>763383</v>
+        <v>762996</v>
       </c>
       <c r="R69" t="n">
-        <v>7306714</v>
+        <v>7306918</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7607,12 +7607,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7623,10 +7623,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119558957</v>
+        <v>119557854</v>
       </c>
       <c r="B70" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7635,25 +7635,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>763026</v>
+        <v>762984</v>
       </c>
       <c r="R70" t="n">
-        <v>7306885</v>
+        <v>7306966</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7713,12 +7713,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7729,10 +7729,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119558967</v>
+        <v>119559017</v>
       </c>
       <c r="B71" t="n">
-        <v>90509</v>
+        <v>97907</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7741,25 +7741,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>763297</v>
+        <v>763421</v>
       </c>
       <c r="R71" t="n">
-        <v>7306876</v>
+        <v>7306683</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7835,7 +7835,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119557854</v>
+        <v>119559018</v>
       </c>
       <c r="B72" t="n">
         <v>97907</v>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>762984</v>
+        <v>763383</v>
       </c>
       <c r="R72" t="n">
-        <v>7306966</v>
+        <v>7306714</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7925,12 +7925,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7941,10 +7941,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119557869</v>
+        <v>119559023</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7953,25 +7953,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>763366</v>
+        <v>762960</v>
       </c>
       <c r="R73" t="n">
-        <v>7306697</v>
+        <v>7306894</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8031,12 +8031,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8047,7 +8047,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119559017</v>
+        <v>119559022</v>
       </c>
       <c r="B74" t="n">
         <v>97907</v>
@@ -8087,10 +8087,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>763421</v>
+        <v>763106</v>
       </c>
       <c r="R74" t="n">
-        <v>7306683</v>
+        <v>7306889</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119558993</v>
+        <v>119558957</v>
       </c>
       <c r="B75" t="n">
-        <v>90916</v>
+        <v>87406</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8165,25 +8165,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1506</v>
+        <v>4412</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>762977</v>
+        <v>763026</v>
       </c>
       <c r="R75" t="n">
-        <v>7306896</v>
+        <v>7306885</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8259,10 +8259,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119558989</v>
+        <v>119559029</v>
       </c>
       <c r="B76" t="n">
-        <v>90846</v>
+        <v>91128</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8271,25 +8271,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>760</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>763410</v>
+        <v>763197</v>
       </c>
       <c r="R76" t="n">
-        <v>7306680</v>
+        <v>7306894</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119558862</v>
+        <v>119558962</v>
       </c>
       <c r="B77" t="n">
-        <v>95455</v>
+        <v>90562</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8381,21 +8381,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>763006</v>
+        <v>763168</v>
       </c>
       <c r="R77" t="n">
-        <v>7306911</v>
+        <v>7306914</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8455,12 +8455,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8577,10 +8577,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119559022</v>
+        <v>119557806</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8589,25 +8589,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>763106</v>
+        <v>763372</v>
       </c>
       <c r="R79" t="n">
-        <v>7306889</v>
+        <v>7306731</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8667,12 +8667,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8683,10 +8683,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119557806</v>
+        <v>119558993</v>
       </c>
       <c r="B80" t="n">
-        <v>79636</v>
+        <v>90916</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8695,25 +8695,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>1506</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>763372</v>
+        <v>762977</v>
       </c>
       <c r="R80" t="n">
-        <v>7306731</v>
+        <v>7306896</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8773,12 +8773,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8789,10 +8789,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119557792</v>
+        <v>119558963</v>
       </c>
       <c r="B81" t="n">
-        <v>87406</v>
+        <v>90562</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8805,21 +8805,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4412</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8829,10 +8829,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>762996</v>
+        <v>763032</v>
       </c>
       <c r="R81" t="n">
-        <v>7306918</v>
+        <v>7306907</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8879,12 +8879,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8895,10 +8895,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119558963</v>
+        <v>119558989</v>
       </c>
       <c r="B82" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>763032</v>
+        <v>763410</v>
       </c>
       <c r="R82" t="n">
-        <v>7306907</v>
+        <v>7306680</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9001,10 +9001,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119558962</v>
+        <v>119559019</v>
       </c>
       <c r="B83" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9013,25 +9013,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>763168</v>
+        <v>763302</v>
       </c>
       <c r="R83" t="n">
-        <v>7306914</v>
+        <v>7306822</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9425,10 +9425,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119559024</v>
+        <v>119558967</v>
       </c>
       <c r="B87" t="n">
-        <v>97907</v>
+        <v>90509</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9437,25 +9437,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>762953</v>
+        <v>763297</v>
       </c>
       <c r="R87" t="n">
-        <v>7306896</v>
+        <v>7306876</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9637,10 +9637,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119559016</v>
+        <v>119557869</v>
       </c>
       <c r="B89" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9649,25 +9649,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9677,10 +9677,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>763454</v>
+        <v>763366</v>
       </c>
       <c r="R89" t="n">
-        <v>7306636</v>
+        <v>7306697</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9727,12 +9727,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9743,7 +9743,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119559019</v>
+        <v>119559024</v>
       </c>
       <c r="B90" t="n">
         <v>97907</v>
@@ -9783,10 +9783,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>763302</v>
+        <v>762953</v>
       </c>
       <c r="R90" t="n">
-        <v>7306822</v>
+        <v>7306896</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9849,7 +9849,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119695010</v>
+        <v>119695009</v>
       </c>
       <c r="B91" t="n">
         <v>79636</v>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>763167</v>
+        <v>763345</v>
       </c>
       <c r="R91" t="n">
-        <v>7306873</v>
+        <v>7306702</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9951,7 +9951,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119695064</v>
+        <v>119695057</v>
       </c>
       <c r="B92" t="n">
         <v>97907</v>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>763050</v>
+        <v>763357</v>
       </c>
       <c r="R92" t="n">
-        <v>7306886</v>
+        <v>7306688</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10053,10 +10053,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119695005</v>
+        <v>119695055</v>
       </c>
       <c r="B93" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10065,25 +10065,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10093,10 +10093,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>763016</v>
+        <v>763391</v>
       </c>
       <c r="R93" t="n">
-        <v>7306911</v>
+        <v>7306668</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10155,7 +10155,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119695059</v>
+        <v>119695064</v>
       </c>
       <c r="B94" t="n">
         <v>97907</v>
@@ -10195,10 +10195,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>763192</v>
+        <v>763050</v>
       </c>
       <c r="R94" t="n">
-        <v>7306872</v>
+        <v>7306886</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10257,7 +10257,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119695065</v>
+        <v>119695066</v>
       </c>
       <c r="B95" t="n">
         <v>97907</v>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>762943</v>
+        <v>762938</v>
       </c>
       <c r="R95" t="n">
-        <v>7306899</v>
+        <v>7306914</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119695066</v>
+        <v>119695062</v>
       </c>
       <c r="B96" t="n">
         <v>97907</v>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>762938</v>
+        <v>763106</v>
       </c>
       <c r="R96" t="n">
-        <v>7306914</v>
+        <v>7306908</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10461,10 +10461,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119695009</v>
+        <v>119695059</v>
       </c>
       <c r="B97" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10473,25 +10473,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>763345</v>
+        <v>763192</v>
       </c>
       <c r="R97" t="n">
-        <v>7306702</v>
+        <v>7306872</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10563,10 +10563,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119695069</v>
+        <v>119695004</v>
       </c>
       <c r="B98" t="n">
-        <v>78526</v>
+        <v>87406</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10579,21 +10579,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>763016</v>
+        <v>763110</v>
       </c>
       <c r="R98" t="n">
-        <v>7306889</v>
+        <v>7306907</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10665,10 +10665,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119695004</v>
+        <v>119695061</v>
       </c>
       <c r="B99" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10677,25 +10677,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10705,10 +10705,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>763110</v>
+        <v>763114</v>
       </c>
       <c r="R99" t="n">
-        <v>7306907</v>
+        <v>7306900</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10767,7 +10767,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119695055</v>
+        <v>119695060</v>
       </c>
       <c r="B100" t="n">
         <v>97907</v>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>763391</v>
+        <v>763155</v>
       </c>
       <c r="R100" t="n">
-        <v>7306668</v>
+        <v>7306883</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10869,7 +10869,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119695056</v>
+        <v>119695058</v>
       </c>
       <c r="B101" t="n">
         <v>97907</v>
@@ -10909,10 +10909,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>763369</v>
+        <v>763283</v>
       </c>
       <c r="R101" t="n">
-        <v>7306687</v>
+        <v>7306863</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119695057</v>
+        <v>119695069</v>
       </c>
       <c r="B102" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10983,25 +10983,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11011,10 +11011,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>763357</v>
+        <v>763016</v>
       </c>
       <c r="R102" t="n">
-        <v>7306688</v>
+        <v>7306889</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11073,10 +11073,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119695063</v>
+        <v>119695010</v>
       </c>
       <c r="B103" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11085,25 +11085,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11113,10 +11113,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>763054</v>
+        <v>763167</v>
       </c>
       <c r="R103" t="n">
-        <v>7306878</v>
+        <v>7306873</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119695062</v>
+        <v>119695063</v>
       </c>
       <c r="B104" t="n">
         <v>97907</v>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>763106</v>
+        <v>763054</v>
       </c>
       <c r="R104" t="n">
-        <v>7306908</v>
+        <v>7306878</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11277,10 +11277,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119695061</v>
+        <v>119695005</v>
       </c>
       <c r="B105" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11289,25 +11289,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>763114</v>
+        <v>763016</v>
       </c>
       <c r="R105" t="n">
-        <v>7306900</v>
+        <v>7306911</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119695058</v>
+        <v>119695056</v>
       </c>
       <c r="B106" t="n">
         <v>97907</v>
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>763283</v>
+        <v>763369</v>
       </c>
       <c r="R106" t="n">
-        <v>7306863</v>
+        <v>7306687</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11481,7 +11481,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119695060</v>
+        <v>119695065</v>
       </c>
       <c r="B107" t="n">
         <v>97907</v>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>763155</v>
+        <v>762943</v>
       </c>
       <c r="R107" t="n">
-        <v>7306883</v>
+        <v>7306899</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -8577,10 +8577,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119557806</v>
+        <v>119558993</v>
       </c>
       <c r="B79" t="n">
-        <v>79636</v>
+        <v>90916</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8589,25 +8589,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>1506</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>763372</v>
+        <v>762977</v>
       </c>
       <c r="R79" t="n">
-        <v>7306731</v>
+        <v>7306896</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8667,12 +8667,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8683,10 +8683,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119558993</v>
+        <v>119557806</v>
       </c>
       <c r="B80" t="n">
-        <v>90916</v>
+        <v>79636</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8695,25 +8695,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1506</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>762977</v>
+        <v>763372</v>
       </c>
       <c r="R80" t="n">
-        <v>7306896</v>
+        <v>7306731</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8773,12 +8773,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8789,10 +8789,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119558963</v>
+        <v>119559019</v>
       </c>
       <c r="B81" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8801,25 +8801,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8829,10 +8829,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>763032</v>
+        <v>763302</v>
       </c>
       <c r="R81" t="n">
-        <v>7306907</v>
+        <v>7306822</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8895,10 +8895,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119558989</v>
+        <v>119558963</v>
       </c>
       <c r="B82" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>763410</v>
+        <v>763032</v>
       </c>
       <c r="R82" t="n">
-        <v>7306680</v>
+        <v>7306907</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9001,10 +9001,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119559019</v>
+        <v>119558989</v>
       </c>
       <c r="B83" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9013,25 +9013,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>763302</v>
+        <v>763410</v>
       </c>
       <c r="R83" t="n">
-        <v>7306822</v>
+        <v>7306680</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9425,10 +9425,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119558967</v>
+        <v>119559021</v>
       </c>
       <c r="B87" t="n">
-        <v>90509</v>
+        <v>97907</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9437,25 +9437,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>763297</v>
+        <v>763222</v>
       </c>
       <c r="R87" t="n">
-        <v>7306876</v>
+        <v>7306894</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9531,10 +9531,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119559021</v>
+        <v>119558967</v>
       </c>
       <c r="B88" t="n">
-        <v>97907</v>
+        <v>90509</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9543,25 +9543,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>763222</v>
+        <v>763297</v>
       </c>
       <c r="R88" t="n">
-        <v>7306894</v>
+        <v>7306876</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -7305,10 +7305,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119559016</v>
+        <v>119559029</v>
       </c>
       <c r="B67" t="n">
-        <v>97907</v>
+        <v>91128</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7321,21 +7321,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>763454</v>
+        <v>763197</v>
       </c>
       <c r="R67" t="n">
-        <v>7306636</v>
+        <v>7306894</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7411,10 +7411,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119558862</v>
+        <v>119559021</v>
       </c>
       <c r="B68" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7423,25 +7423,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>763006</v>
+        <v>763222</v>
       </c>
       <c r="R68" t="n">
-        <v>7306911</v>
+        <v>7306894</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7501,12 +7501,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7517,10 +7517,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119557792</v>
+        <v>119557856</v>
       </c>
       <c r="B69" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7529,25 +7529,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7560,7 +7560,7 @@
         <v>762996</v>
       </c>
       <c r="R69" t="n">
-        <v>7306918</v>
+        <v>7306937</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119557854</v>
+        <v>119559019</v>
       </c>
       <c r="B70" t="n">
         <v>97907</v>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>762984</v>
+        <v>763302</v>
       </c>
       <c r="R70" t="n">
-        <v>7306966</v>
+        <v>7306822</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7713,12 +7713,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7729,7 +7729,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119559017</v>
+        <v>119559018</v>
       </c>
       <c r="B71" t="n">
         <v>97907</v>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>763421</v>
+        <v>763383</v>
       </c>
       <c r="R71" t="n">
-        <v>7306683</v>
+        <v>7306714</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7835,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119559018</v>
+        <v>119557792</v>
       </c>
       <c r="B72" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7847,25 +7847,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>763383</v>
+        <v>762996</v>
       </c>
       <c r="R72" t="n">
-        <v>7306714</v>
+        <v>7306918</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7925,12 +7925,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7941,10 +7941,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119559023</v>
+        <v>119558967</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
+        <v>90509</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7953,25 +7953,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>762960</v>
+        <v>763297</v>
       </c>
       <c r="R73" t="n">
-        <v>7306894</v>
+        <v>7306876</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119558957</v>
+        <v>119559017</v>
       </c>
       <c r="B75" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8165,25 +8165,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>763026</v>
+        <v>763421</v>
       </c>
       <c r="R75" t="n">
-        <v>7306885</v>
+        <v>7306683</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8259,10 +8259,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119559029</v>
+        <v>119557806</v>
       </c>
       <c r="B76" t="n">
-        <v>91128</v>
+        <v>79636</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8271,25 +8271,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>763197</v>
+        <v>763372</v>
       </c>
       <c r="R76" t="n">
-        <v>7306894</v>
+        <v>7306731</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8349,12 +8349,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8365,10 +8365,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119558962</v>
+        <v>119559028</v>
       </c>
       <c r="B77" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8381,21 +8381,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>763168</v>
+        <v>762957</v>
       </c>
       <c r="R77" t="n">
-        <v>7306914</v>
+        <v>7306896</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8471,10 +8471,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119559020</v>
+        <v>119558993</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>90916</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8487,21 +8487,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>1506</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8511,10 +8511,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>763292</v>
+        <v>762977</v>
       </c>
       <c r="R78" t="n">
-        <v>7306865</v>
+        <v>7306896</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8577,10 +8577,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119558993</v>
+        <v>119559020</v>
       </c>
       <c r="B79" t="n">
-        <v>90916</v>
+        <v>97907</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8593,21 +8593,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>762977</v>
+        <v>763292</v>
       </c>
       <c r="R79" t="n">
-        <v>7306896</v>
+        <v>7306865</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8683,10 +8683,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119557806</v>
+        <v>119557854</v>
       </c>
       <c r="B80" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8695,25 +8695,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>763372</v>
+        <v>762984</v>
       </c>
       <c r="R80" t="n">
-        <v>7306731</v>
+        <v>7306966</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8789,10 +8789,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119559019</v>
+        <v>119558862</v>
       </c>
       <c r="B81" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8801,25 +8801,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8829,10 +8829,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>763302</v>
+        <v>763006</v>
       </c>
       <c r="R81" t="n">
-        <v>7306822</v>
+        <v>7306911</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8879,12 +8879,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8895,10 +8895,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119558963</v>
+        <v>119559023</v>
       </c>
       <c r="B82" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8907,25 +8907,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>763032</v>
+        <v>762960</v>
       </c>
       <c r="R82" t="n">
-        <v>7306907</v>
+        <v>7306894</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9001,10 +9001,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119558989</v>
+        <v>119558963</v>
       </c>
       <c r="B83" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>763410</v>
+        <v>763032</v>
       </c>
       <c r="R83" t="n">
-        <v>7306680</v>
+        <v>7306907</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9107,7 +9107,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119557856</v>
+        <v>119559016</v>
       </c>
       <c r="B84" t="n">
         <v>97907</v>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>762996</v>
+        <v>763454</v>
       </c>
       <c r="R84" t="n">
-        <v>7306937</v>
+        <v>7306636</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9197,12 +9197,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9213,10 +9213,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119559028</v>
+        <v>119558962</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9229,21 +9229,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>762957</v>
+        <v>763168</v>
       </c>
       <c r="R85" t="n">
-        <v>7306896</v>
+        <v>7306914</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9319,10 +9319,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119558863</v>
+        <v>119557869</v>
       </c>
       <c r="B86" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9335,21 +9335,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9359,10 +9359,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>762972</v>
+        <v>763366</v>
       </c>
       <c r="R86" t="n">
-        <v>7306899</v>
+        <v>7306697</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9409,12 +9409,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9425,10 +9425,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119559021</v>
+        <v>119558989</v>
       </c>
       <c r="B87" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9437,25 +9437,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>763222</v>
+        <v>763410</v>
       </c>
       <c r="R87" t="n">
-        <v>7306894</v>
+        <v>7306680</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9531,10 +9531,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119558967</v>
+        <v>119558957</v>
       </c>
       <c r="B88" t="n">
-        <v>90509</v>
+        <v>87406</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9547,21 +9547,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>112</v>
+        <v>4412</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>763297</v>
+        <v>763026</v>
       </c>
       <c r="R88" t="n">
-        <v>7306876</v>
+        <v>7306885</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9637,10 +9637,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119557869</v>
+        <v>119558863</v>
       </c>
       <c r="B89" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9653,21 +9653,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9677,10 +9677,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>763366</v>
+        <v>762972</v>
       </c>
       <c r="R89" t="n">
-        <v>7306697</v>
+        <v>7306899</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9727,12 +9727,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9849,10 +9849,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119695009</v>
+        <v>119695058</v>
       </c>
       <c r="B91" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9861,25 +9861,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>763345</v>
+        <v>763283</v>
       </c>
       <c r="R91" t="n">
-        <v>7306702</v>
+        <v>7306863</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9951,7 +9951,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119695057</v>
+        <v>119695055</v>
       </c>
       <c r="B92" t="n">
         <v>97907</v>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>763357</v>
+        <v>763391</v>
       </c>
       <c r="R92" t="n">
-        <v>7306688</v>
+        <v>7306668</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10053,7 +10053,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119695055</v>
+        <v>119695057</v>
       </c>
       <c r="B93" t="n">
         <v>97907</v>
@@ -10093,10 +10093,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>763391</v>
+        <v>763357</v>
       </c>
       <c r="R93" t="n">
-        <v>7306668</v>
+        <v>7306688</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10155,7 +10155,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119695064</v>
+        <v>119695060</v>
       </c>
       <c r="B94" t="n">
         <v>97907</v>
@@ -10195,10 +10195,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>763050</v>
+        <v>763155</v>
       </c>
       <c r="R94" t="n">
-        <v>7306886</v>
+        <v>7306883</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10257,10 +10257,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119695066</v>
+        <v>119695005</v>
       </c>
       <c r="B95" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10269,25 +10269,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>762938</v>
+        <v>763016</v>
       </c>
       <c r="R95" t="n">
-        <v>7306914</v>
+        <v>7306911</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10461,10 +10461,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119695059</v>
+        <v>119695009</v>
       </c>
       <c r="B97" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10473,25 +10473,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>763192</v>
+        <v>763345</v>
       </c>
       <c r="R97" t="n">
-        <v>7306872</v>
+        <v>7306702</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10563,10 +10563,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119695004</v>
+        <v>119695056</v>
       </c>
       <c r="B98" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10575,25 +10575,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>763110</v>
+        <v>763369</v>
       </c>
       <c r="R98" t="n">
-        <v>7306907</v>
+        <v>7306687</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10665,10 +10665,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119695061</v>
+        <v>119695004</v>
       </c>
       <c r="B99" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10677,25 +10677,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10705,10 +10705,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>763114</v>
+        <v>763110</v>
       </c>
       <c r="R99" t="n">
-        <v>7306900</v>
+        <v>7306907</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10767,10 +10767,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119695060</v>
+        <v>119695010</v>
       </c>
       <c r="B100" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10779,25 +10779,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>763155</v>
+        <v>763167</v>
       </c>
       <c r="R100" t="n">
-        <v>7306883</v>
+        <v>7306873</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10869,7 +10869,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119695058</v>
+        <v>119695066</v>
       </c>
       <c r="B101" t="n">
         <v>97907</v>
@@ -10909,10 +10909,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>763283</v>
+        <v>762938</v>
       </c>
       <c r="R101" t="n">
-        <v>7306863</v>
+        <v>7306914</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119695069</v>
+        <v>119695065</v>
       </c>
       <c r="B102" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10983,25 +10983,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11011,10 +11011,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>763016</v>
+        <v>762943</v>
       </c>
       <c r="R102" t="n">
-        <v>7306889</v>
+        <v>7306899</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11073,10 +11073,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119695010</v>
+        <v>119695069</v>
       </c>
       <c r="B103" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11085,25 +11085,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11113,10 +11113,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>763167</v>
+        <v>763016</v>
       </c>
       <c r="R103" t="n">
-        <v>7306873</v>
+        <v>7306889</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119695063</v>
+        <v>119695064</v>
       </c>
       <c r="B104" t="n">
         <v>97907</v>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>763054</v>
+        <v>763050</v>
       </c>
       <c r="R104" t="n">
-        <v>7306878</v>
+        <v>7306886</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11277,10 +11277,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119695005</v>
+        <v>119695063</v>
       </c>
       <c r="B105" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11289,25 +11289,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>763016</v>
+        <v>763054</v>
       </c>
       <c r="R105" t="n">
-        <v>7306911</v>
+        <v>7306878</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119695056</v>
+        <v>119695061</v>
       </c>
       <c r="B106" t="n">
         <v>97907</v>
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>763369</v>
+        <v>763114</v>
       </c>
       <c r="R106" t="n">
-        <v>7306687</v>
+        <v>7306900</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11481,7 +11481,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119695065</v>
+        <v>119695059</v>
       </c>
       <c r="B107" t="n">
         <v>97907</v>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>762943</v>
+        <v>763192</v>
       </c>
       <c r="R107" t="n">
-        <v>7306899</v>
+        <v>7306872</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -9319,10 +9319,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119557869</v>
+        <v>119558989</v>
       </c>
       <c r="B86" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9335,21 +9335,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9359,10 +9359,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>763366</v>
+        <v>763410</v>
       </c>
       <c r="R86" t="n">
-        <v>7306697</v>
+        <v>7306680</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9409,12 +9409,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9425,10 +9425,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119558989</v>
+        <v>119557869</v>
       </c>
       <c r="B87" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9441,21 +9441,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>763410</v>
+        <v>763366</v>
       </c>
       <c r="R87" t="n">
-        <v>7306680</v>
+        <v>7306697</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9515,12 +9515,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -9951,7 +9951,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119695055</v>
+        <v>119695059</v>
       </c>
       <c r="B92" t="n">
         <v>97907</v>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>763391</v>
+        <v>763192</v>
       </c>
       <c r="R92" t="n">
-        <v>7306668</v>
+        <v>7306872</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10053,10 +10053,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119695057</v>
+        <v>119695069</v>
       </c>
       <c r="B93" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10065,25 +10065,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10093,10 +10093,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>763357</v>
+        <v>763016</v>
       </c>
       <c r="R93" t="n">
-        <v>7306688</v>
+        <v>7306889</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10155,10 +10155,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119695060</v>
+        <v>119695005</v>
       </c>
       <c r="B94" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10167,25 +10167,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10195,10 +10195,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>763155</v>
+        <v>763016</v>
       </c>
       <c r="R94" t="n">
-        <v>7306883</v>
+        <v>7306911</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10257,10 +10257,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119695005</v>
+        <v>119695064</v>
       </c>
       <c r="B95" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10269,25 +10269,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>763016</v>
+        <v>763050</v>
       </c>
       <c r="R95" t="n">
-        <v>7306911</v>
+        <v>7306886</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10359,10 +10359,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119695062</v>
+        <v>119695010</v>
       </c>
       <c r="B96" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10371,25 +10371,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>763106</v>
+        <v>763167</v>
       </c>
       <c r="R96" t="n">
-        <v>7306908</v>
+        <v>7306873</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10461,10 +10461,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119695009</v>
+        <v>119695066</v>
       </c>
       <c r="B97" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10473,25 +10473,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>763345</v>
+        <v>762938</v>
       </c>
       <c r="R97" t="n">
-        <v>7306702</v>
+        <v>7306914</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10563,7 +10563,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119695056</v>
+        <v>119695061</v>
       </c>
       <c r="B98" t="n">
         <v>97907</v>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>763369</v>
+        <v>763114</v>
       </c>
       <c r="R98" t="n">
-        <v>7306687</v>
+        <v>7306900</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10665,10 +10665,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119695004</v>
+        <v>119695056</v>
       </c>
       <c r="B99" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10677,25 +10677,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10705,10 +10705,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>763110</v>
+        <v>763369</v>
       </c>
       <c r="R99" t="n">
-        <v>7306907</v>
+        <v>7306687</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10767,7 +10767,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119695010</v>
+        <v>119695009</v>
       </c>
       <c r="B100" t="n">
         <v>79636</v>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>763167</v>
+        <v>763345</v>
       </c>
       <c r="R100" t="n">
-        <v>7306873</v>
+        <v>7306702</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10869,7 +10869,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119695066</v>
+        <v>119695065</v>
       </c>
       <c r="B101" t="n">
         <v>97907</v>
@@ -10909,10 +10909,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>762938</v>
+        <v>762943</v>
       </c>
       <c r="R101" t="n">
-        <v>7306914</v>
+        <v>7306899</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10971,7 +10971,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119695065</v>
+        <v>119695063</v>
       </c>
       <c r="B102" t="n">
         <v>97907</v>
@@ -11011,10 +11011,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>762943</v>
+        <v>763054</v>
       </c>
       <c r="R102" t="n">
-        <v>7306899</v>
+        <v>7306878</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11073,10 +11073,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119695069</v>
+        <v>119695060</v>
       </c>
       <c r="B103" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11085,25 +11085,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11113,10 +11113,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>763016</v>
+        <v>763155</v>
       </c>
       <c r="R103" t="n">
-        <v>7306889</v>
+        <v>7306883</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119695064</v>
+        <v>119695062</v>
       </c>
       <c r="B104" t="n">
         <v>97907</v>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>763050</v>
+        <v>763106</v>
       </c>
       <c r="R104" t="n">
-        <v>7306886</v>
+        <v>7306908</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11277,10 +11277,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119695063</v>
+        <v>119695004</v>
       </c>
       <c r="B105" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11289,25 +11289,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>763054</v>
+        <v>763110</v>
       </c>
       <c r="R105" t="n">
-        <v>7306878</v>
+        <v>7306907</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119695061</v>
+        <v>119695057</v>
       </c>
       <c r="B106" t="n">
         <v>97907</v>
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>763114</v>
+        <v>763357</v>
       </c>
       <c r="R106" t="n">
-        <v>7306900</v>
+        <v>7306688</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11481,7 +11481,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119695059</v>
+        <v>119695055</v>
       </c>
       <c r="B107" t="n">
         <v>97907</v>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>763192</v>
+        <v>763391</v>
       </c>
       <c r="R107" t="n">
-        <v>7306872</v>
+        <v>7306668</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -9951,10 +9951,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119695059</v>
+        <v>119695069</v>
       </c>
       <c r="B92" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9963,25 +9963,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>763192</v>
+        <v>763016</v>
       </c>
       <c r="R92" t="n">
-        <v>7306872</v>
+        <v>7306889</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10053,10 +10053,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119695069</v>
+        <v>119695059</v>
       </c>
       <c r="B93" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10065,25 +10065,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10093,10 +10093,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>763016</v>
+        <v>763192</v>
       </c>
       <c r="R93" t="n">
-        <v>7306889</v>
+        <v>7306872</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -9951,10 +9951,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119695069</v>
+        <v>119695059</v>
       </c>
       <c r="B92" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9963,25 +9963,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>763016</v>
+        <v>763192</v>
       </c>
       <c r="R92" t="n">
-        <v>7306889</v>
+        <v>7306872</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10053,10 +10053,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119695059</v>
+        <v>119695069</v>
       </c>
       <c r="B93" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10065,25 +10065,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10093,10 +10093,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>763192</v>
+        <v>763016</v>
       </c>
       <c r="R93" t="n">
-        <v>7306872</v>
+        <v>7306889</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113477188</v>
+        <v>113477203</v>
       </c>
       <c r="B2" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763380</v>
+        <v>763549</v>
       </c>
       <c r="R2" t="n">
-        <v>7306816</v>
+        <v>7306818</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113477222</v>
+        <v>119558862</v>
       </c>
       <c r="B3" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763611</v>
+        <v>763006</v>
       </c>
       <c r="R3" t="n">
-        <v>7306628</v>
+        <v>7306911</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +857,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113477227</v>
+        <v>119558967</v>
       </c>
       <c r="B4" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +908,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763556</v>
+        <v>763297</v>
       </c>
       <c r="R4" t="n">
-        <v>7306813</v>
+        <v>7306876</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +958,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113477174</v>
+        <v>113477173</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>763612</v>
+        <v>763257</v>
       </c>
       <c r="R5" t="n">
-        <v>7306628</v>
+        <v>7306949</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,15 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113477234</v>
+        <v>113477176</v>
       </c>
       <c r="B6" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,12 +1091,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763546</v>
+        <v>763485</v>
       </c>
       <c r="R6" t="n">
-        <v>7306828</v>
+        <v>7306838</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,15 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113477176</v>
+        <v>113477185</v>
       </c>
       <c r="B7" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,12 +1188,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763485</v>
+        <v>763524</v>
       </c>
       <c r="R7" t="n">
-        <v>7306838</v>
+        <v>7306840</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,15 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113477173</v>
+        <v>113477187</v>
       </c>
       <c r="B8" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,12 +1285,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>763257</v>
+        <v>762965</v>
       </c>
       <c r="R8" t="n">
-        <v>7306949</v>
+        <v>7306853</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,15 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113477231</v>
+        <v>113477188</v>
       </c>
       <c r="B9" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>763544</v>
+        <v>763380</v>
       </c>
       <c r="R9" t="n">
-        <v>7306834</v>
+        <v>7306816</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1459,12 +1427,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,15 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113477189</v>
+        <v>113477214</v>
       </c>
       <c r="B10" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1470,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>763345</v>
+        <v>763547</v>
       </c>
       <c r="R10" t="n">
-        <v>7306788</v>
+        <v>7306822</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,12 +1524,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,15 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113477225</v>
+        <v>113477222</v>
       </c>
       <c r="B11" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>763622</v>
+        <v>763611</v>
       </c>
       <c r="R11" t="n">
-        <v>7306786</v>
+        <v>7306628</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1663,12 +1621,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,15 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113477204</v>
+        <v>113477234</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763403</v>
+        <v>763546</v>
       </c>
       <c r="R12" t="n">
-        <v>7306831</v>
+        <v>7306828</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,15 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113477194</v>
+        <v>119558989</v>
       </c>
       <c r="B13" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1761,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1785,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>763370</v>
+        <v>763410</v>
       </c>
       <c r="R13" t="n">
-        <v>7306956</v>
+        <v>7306680</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1867,12 +1815,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,27 +1835,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113477232</v>
+        <v>130828516</v>
       </c>
       <c r="B14" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1862,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,13 +1886,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>763465</v>
+        <v>763330</v>
       </c>
       <c r="R14" t="n">
-        <v>7306863</v>
+        <v>7306842</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1969,12 +1916,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1983,13 +1930,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2001,37 +1954,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113477218</v>
+        <v>119559029</v>
       </c>
       <c r="B15" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +1989,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762954</v>
+        <v>763197</v>
       </c>
       <c r="R15" t="n">
-        <v>7306858</v>
+        <v>7306894</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,12 +2019,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,27 +2039,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113477195</v>
+        <v>113477177</v>
       </c>
       <c r="B16" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762965</v>
+        <v>763480</v>
       </c>
       <c r="R16" t="n">
-        <v>7306905</v>
+        <v>7306840</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,15 +2152,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113477221</v>
+        <v>113477195</v>
       </c>
       <c r="B17" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>763096</v>
+        <v>762965</v>
       </c>
       <c r="R17" t="n">
-        <v>7306814</v>
+        <v>7306905</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,15 +2249,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113477233</v>
+        <v>113477209</v>
       </c>
       <c r="B18" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763142</v>
+        <v>762963</v>
       </c>
       <c r="R18" t="n">
-        <v>7306903</v>
+        <v>7306865</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,12 +2314,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,15 +2346,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113477223</v>
+        <v>113477221</v>
       </c>
       <c r="B19" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763331</v>
+        <v>763096</v>
       </c>
       <c r="R19" t="n">
-        <v>7306850</v>
+        <v>7306814</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,15 +2443,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113477185</v>
+        <v>113477223</v>
       </c>
       <c r="B20" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,21 +2454,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2478,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>763524</v>
+        <v>763331</v>
       </c>
       <c r="R20" t="n">
-        <v>7306840</v>
+        <v>7306850</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,15 +2540,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113477237</v>
+        <v>113477231</v>
       </c>
       <c r="B21" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2551,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2575,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>763601</v>
+        <v>763544</v>
       </c>
       <c r="R21" t="n">
-        <v>7306790</v>
+        <v>7306834</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2715,15 +2637,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113477183</v>
+        <v>113477232</v>
       </c>
       <c r="B22" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,21 +2648,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2672,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>763150</v>
+        <v>763465</v>
       </c>
       <c r="R22" t="n">
-        <v>7306869</v>
+        <v>7306863</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2817,37 +2734,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113477247</v>
+        <v>113477233</v>
       </c>
       <c r="B23" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>762978</v>
+        <v>763142</v>
       </c>
       <c r="R23" t="n">
-        <v>7306910</v>
+        <v>7306903</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2887,12 +2799,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2919,15 +2831,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113477177</v>
+        <v>113477254</v>
       </c>
       <c r="B24" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,10 +2866,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>763480</v>
+        <v>763254</v>
       </c>
       <c r="R24" t="n">
-        <v>7306840</v>
+        <v>7306946</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3021,37 +2928,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113477217</v>
+        <v>113627223</v>
       </c>
       <c r="B25" t="n">
-        <v>90774</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,13 +2963,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>763334</v>
+        <v>763380</v>
       </c>
       <c r="R25" t="n">
-        <v>7306846</v>
+        <v>7306687</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3091,12 +2993,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3111,27 +3013,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113477186</v>
+        <v>119558863</v>
       </c>
       <c r="B26" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,21 +3036,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,13 +3060,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>763284</v>
+        <v>762972</v>
       </c>
       <c r="R26" t="n">
-        <v>7306852</v>
+        <v>7306899</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3193,12 +3090,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,27 +3110,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113477254</v>
+        <v>119558962</v>
       </c>
       <c r="B27" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,13 +3161,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>763254</v>
+        <v>763168</v>
       </c>
       <c r="R27" t="n">
-        <v>7306946</v>
+        <v>7306914</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3295,12 +3191,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3315,27 +3211,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113477242</v>
+        <v>119558963</v>
       </c>
       <c r="B28" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3343,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,13 +3262,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>763500</v>
+        <v>763032</v>
       </c>
       <c r="R28" t="n">
-        <v>7306846</v>
+        <v>7306907</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3397,12 +3292,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3417,27 +3312,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113477209</v>
+        <v>113477217</v>
       </c>
       <c r="B29" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3445,21 +3339,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3363,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>762963</v>
+        <v>763334</v>
       </c>
       <c r="R29" t="n">
-        <v>7306865</v>
+        <v>7306846</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3531,37 +3425,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113477214</v>
+        <v>119558993</v>
       </c>
       <c r="B30" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,13 +3460,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>763547</v>
+        <v>762977</v>
       </c>
       <c r="R30" t="n">
-        <v>7306822</v>
+        <v>7306896</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3601,12 +3490,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3621,27 +3510,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113477187</v>
+        <v>119557792</v>
       </c>
       <c r="B31" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3649,21 +3537,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>4412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,13 +3561,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>762965</v>
+        <v>762996</v>
       </c>
       <c r="R31" t="n">
-        <v>7306853</v>
+        <v>7306918</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3703,12 +3591,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3723,49 +3611,48 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113477203</v>
+        <v>119558957</v>
       </c>
       <c r="B32" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>48</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,13 +3662,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>763549</v>
+        <v>763026</v>
       </c>
       <c r="R32" t="n">
-        <v>7306818</v>
+        <v>7306885</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3805,12 +3692,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3825,65 +3712,64 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113627242</v>
+        <v>119695004</v>
       </c>
       <c r="B33" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>4412</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fällforsen, Nb</t>
+          <t>S Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>763269</v>
+        <v>763110</v>
       </c>
       <c r="R33" t="n">
-        <v>7306759</v>
+        <v>7306907</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3907,12 +3793,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3927,27 +3813,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113627264</v>
+        <v>119695005</v>
       </c>
       <c r="B34" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3955,37 +3836,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fällforsen, Nb</t>
+          <t>S Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>763249</v>
+        <v>763016</v>
       </c>
       <c r="R34" t="n">
-        <v>7306837</v>
+        <v>7306911</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4009,12 +3890,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4029,31 +3910,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113627263</v>
+        <v>113477204</v>
       </c>
       <c r="B35" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4081,13 +3957,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>763243</v>
+        <v>763403</v>
       </c>
       <c r="R35" t="n">
         <v>7306831</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4111,12 +3987,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4131,49 +4007,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113627224</v>
+        <v>113477242</v>
       </c>
       <c r="B36" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,13 +4054,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>763515</v>
+        <v>763500</v>
       </c>
       <c r="R36" t="n">
-        <v>7306778</v>
+        <v>7306846</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4213,12 +4084,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4233,49 +4104,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113627225</v>
+        <v>113627257</v>
       </c>
       <c r="B37" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4151,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>763488</v>
+        <v>763461</v>
       </c>
       <c r="R37" t="n">
-        <v>7306869</v>
+        <v>7306643</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4347,37 +4213,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113627229</v>
+        <v>113627258</v>
       </c>
       <c r="B38" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4248,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>763381</v>
+        <v>763288</v>
       </c>
       <c r="R38" t="n">
-        <v>7306679</v>
+        <v>7306758</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4449,37 +4310,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113627230</v>
+        <v>113627259</v>
       </c>
       <c r="B39" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4345,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>763281</v>
+        <v>763286</v>
       </c>
       <c r="R39" t="n">
-        <v>7306769</v>
+        <v>7306759</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4551,37 +4407,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113627241</v>
+        <v>113627260</v>
       </c>
       <c r="B40" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4442,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>763469</v>
+        <v>763257</v>
       </c>
       <c r="R40" t="n">
-        <v>7306934</v>
+        <v>7306752</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4653,19 +4504,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113627257</v>
+        <v>113627261</v>
       </c>
       <c r="B41" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4693,10 +4539,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>763461</v>
+        <v>763228</v>
       </c>
       <c r="R41" t="n">
-        <v>7306643</v>
+        <v>7306751</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4755,37 +4601,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113627244</v>
+        <v>113627262</v>
       </c>
       <c r="B42" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4636,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>763468</v>
+        <v>763213</v>
       </c>
       <c r="R42" t="n">
-        <v>7306669</v>
+        <v>7306793</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4857,37 +4698,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113627232</v>
+        <v>113627263</v>
       </c>
       <c r="B43" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4733,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>763215</v>
+        <v>763243</v>
       </c>
       <c r="R43" t="n">
-        <v>7306756</v>
+        <v>7306831</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4959,37 +4795,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113627233</v>
+        <v>113627264</v>
       </c>
       <c r="B44" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4830,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>763215</v>
+        <v>763249</v>
       </c>
       <c r="R44" t="n">
-        <v>7306798</v>
+        <v>7306837</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5061,37 +4892,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113627223</v>
+        <v>113627265</v>
       </c>
       <c r="B45" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +4927,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>763380</v>
+        <v>763257</v>
       </c>
       <c r="R45" t="n">
-        <v>7306687</v>
+        <v>7306838</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5163,37 +4989,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113627234</v>
+        <v>113627266</v>
       </c>
       <c r="B46" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5203,10 +5024,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>763248</v>
+        <v>763275</v>
       </c>
       <c r="R46" t="n">
-        <v>7306836</v>
+        <v>7306841</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5265,19 +5086,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113627261</v>
+        <v>119557869</v>
       </c>
       <c r="B47" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5305,13 +5121,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>763228</v>
+        <v>763366</v>
       </c>
       <c r="R47" t="n">
-        <v>7306751</v>
+        <v>7306697</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5335,12 +5151,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5355,49 +5171,48 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113627252</v>
+        <v>119559028</v>
       </c>
       <c r="B48" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,13 +5222,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>763492</v>
+        <v>762957</v>
       </c>
       <c r="R48" t="n">
-        <v>7306745</v>
+        <v>7306896</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5437,12 +5252,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5457,65 +5272,64 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113627238</v>
+        <v>119695069</v>
       </c>
       <c r="B49" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fällforsen, Nb</t>
+          <t>S Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>763385</v>
+        <v>763016</v>
       </c>
       <c r="R49" t="n">
-        <v>7306919</v>
+        <v>7306889</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5539,12 +5353,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5559,49 +5373,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113627258</v>
+        <v>113477247</v>
       </c>
       <c r="B50" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,13 +5420,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>763288</v>
+        <v>762978</v>
       </c>
       <c r="R50" t="n">
-        <v>7306758</v>
+        <v>7306910</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5641,12 +5450,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5661,27 +5470,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113627259</v>
+        <v>113477189</v>
       </c>
       <c r="B51" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5689,21 +5493,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,13 +5517,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>763286</v>
+        <v>763345</v>
       </c>
       <c r="R51" t="n">
-        <v>7306759</v>
+        <v>7306788</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5743,12 +5547,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5763,27 +5567,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113627237</v>
+        <v>113477225</v>
       </c>
       <c r="B52" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5791,21 +5590,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,13 +5614,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>763371</v>
+        <v>763622</v>
       </c>
       <c r="R52" t="n">
-        <v>7306912</v>
+        <v>7306786</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5845,12 +5644,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5865,27 +5664,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113627246</v>
+        <v>113627252</v>
       </c>
       <c r="B53" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5893,21 +5687,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5917,10 +5711,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>763416</v>
+        <v>763492</v>
       </c>
       <c r="R53" t="n">
-        <v>7306668</v>
+        <v>7306745</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5979,37 +5773,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113627260</v>
+        <v>113627241</v>
       </c>
       <c r="B54" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6019,10 +5808,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>763257</v>
+        <v>763469</v>
       </c>
       <c r="R54" t="n">
-        <v>7306752</v>
+        <v>7306934</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6081,37 +5870,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113627245</v>
+        <v>113627242</v>
       </c>
       <c r="B55" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6121,10 +5905,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>763488</v>
+        <v>763269</v>
       </c>
       <c r="R55" t="n">
-        <v>7306829</v>
+        <v>7306759</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6183,37 +5967,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113627236</v>
+        <v>119557806</v>
       </c>
       <c r="B56" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,13 +6002,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>763325</v>
+        <v>763372</v>
       </c>
       <c r="R56" t="n">
-        <v>7306890</v>
+        <v>7306731</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6253,12 +6032,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6273,65 +6052,64 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113627227</v>
+        <v>119695009</v>
       </c>
       <c r="B57" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fällforsen, Nb</t>
+          <t>S Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>763494</v>
+        <v>763345</v>
       </c>
       <c r="R57" t="n">
-        <v>7306758</v>
+        <v>7306702</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6355,12 +6133,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6375,65 +6153,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113627235</v>
+        <v>119695010</v>
       </c>
       <c r="B58" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fällforsen, Nb</t>
+          <t>S Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>763277</v>
+        <v>763167</v>
       </c>
       <c r="R58" t="n">
-        <v>7306835</v>
+        <v>7306873</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6457,12 +6230,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6477,49 +6250,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113627266</v>
+        <v>113477174</v>
       </c>
       <c r="B59" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,13 +6297,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>763275</v>
+        <v>763612</v>
       </c>
       <c r="R59" t="n">
-        <v>7306841</v>
+        <v>7306628</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6559,12 +6327,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6579,44 +6347,39 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113627228</v>
+        <v>113477180</v>
       </c>
       <c r="B60" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6631,13 +6394,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>763469</v>
+        <v>763489</v>
       </c>
       <c r="R60" t="n">
-        <v>7306655</v>
+        <v>7306621</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6661,12 +6424,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6681,49 +6444,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113627262</v>
+        <v>113627244</v>
       </c>
       <c r="B61" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6491,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>763213</v>
+        <v>763468</v>
       </c>
       <c r="R61" t="n">
-        <v>7306793</v>
+        <v>7306669</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6795,37 +6553,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113627265</v>
+        <v>113627245</v>
       </c>
       <c r="B62" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6835,10 +6588,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>763257</v>
+        <v>763488</v>
       </c>
       <c r="R62" t="n">
-        <v>7306838</v>
+        <v>7306829</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6897,32 +6650,27 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113627231</v>
+        <v>113627246</v>
       </c>
       <c r="B63" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6937,10 +6685,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>763228</v>
+        <v>763416</v>
       </c>
       <c r="R63" t="n">
-        <v>7306736</v>
+        <v>7306668</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6999,32 +6747,27 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113627243</v>
+        <v>113627270</v>
       </c>
       <c r="B64" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7039,10 +6782,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>763506</v>
+        <v>763439</v>
       </c>
       <c r="R64" t="n">
-        <v>7306778</v>
+        <v>7306637</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7101,15 +6844,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113627239</v>
+        <v>113477186</v>
       </c>
       <c r="B65" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7141,13 +6879,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>763382</v>
+        <v>763284</v>
       </c>
       <c r="R65" t="n">
-        <v>7306989</v>
+        <v>7306852</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7171,12 +6909,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7191,27 +6929,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113627226</v>
+        <v>113477194</v>
       </c>
       <c r="B66" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7243,13 +6976,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>763484</v>
+        <v>763370</v>
       </c>
       <c r="R66" t="n">
-        <v>7306849</v>
+        <v>7306956</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7273,12 +7006,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7293,49 +7026,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119559029</v>
+        <v>113477237</v>
       </c>
       <c r="B67" t="n">
-        <v>91128</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7345,13 +7073,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>763197</v>
+        <v>763601</v>
       </c>
       <c r="R67" t="n">
-        <v>7306894</v>
+        <v>7306790</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7375,12 +7103,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7395,53 +7123,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Adam Helleberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119559021</v>
+        <v>113627224</v>
       </c>
       <c r="B68" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7451,13 +7170,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>763222</v>
+        <v>763515</v>
       </c>
       <c r="R68" t="n">
-        <v>7306894</v>
+        <v>7306778</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7481,12 +7200,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7501,53 +7220,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119557856</v>
+        <v>113627225</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7557,13 +7267,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>762996</v>
+        <v>763488</v>
       </c>
       <c r="R69" t="n">
-        <v>7306937</v>
+        <v>7306869</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7587,12 +7297,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,53 +7317,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119559019</v>
+        <v>113627226</v>
       </c>
       <c r="B70" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7663,13 +7364,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>763302</v>
+        <v>763484</v>
       </c>
       <c r="R70" t="n">
-        <v>7306822</v>
+        <v>7306849</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7693,12 +7394,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7713,53 +7414,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119559018</v>
+        <v>113627227</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7769,13 +7461,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>763383</v>
+        <v>763494</v>
       </c>
       <c r="R71" t="n">
-        <v>7306714</v>
+        <v>7306758</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7799,12 +7491,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7819,31 +7511,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119557792</v>
+        <v>113627228</v>
       </c>
       <c r="B72" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7851,21 +7534,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,13 +7558,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>762996</v>
+        <v>763469</v>
       </c>
       <c r="R72" t="n">
-        <v>7306918</v>
+        <v>7306655</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7905,12 +7588,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7925,31 +7608,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119558967</v>
+        <v>113627229</v>
       </c>
       <c r="B73" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7957,21 +7631,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7981,13 +7655,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>763297</v>
+        <v>763381</v>
       </c>
       <c r="R73" t="n">
-        <v>7306876</v>
+        <v>7306679</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8011,12 +7685,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8031,53 +7705,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119559022</v>
+        <v>113627230</v>
       </c>
       <c r="B74" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8087,13 +7752,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>763106</v>
+        <v>763281</v>
       </c>
       <c r="R74" t="n">
-        <v>7306889</v>
+        <v>7306769</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8117,12 +7782,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8137,53 +7802,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119559017</v>
+        <v>113627231</v>
       </c>
       <c r="B75" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8193,13 +7849,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>763421</v>
+        <v>763228</v>
       </c>
       <c r="R75" t="n">
-        <v>7306683</v>
+        <v>7306736</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8223,12 +7879,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8243,53 +7899,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119557806</v>
+        <v>113627232</v>
       </c>
       <c r="B76" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8299,13 +7946,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>763372</v>
+        <v>763215</v>
       </c>
       <c r="R76" t="n">
-        <v>7306731</v>
+        <v>7306756</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8329,12 +7976,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8349,31 +7996,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119559028</v>
+        <v>113627233</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8381,21 +8019,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8405,13 +8043,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>762957</v>
+        <v>763215</v>
       </c>
       <c r="R77" t="n">
-        <v>7306896</v>
+        <v>7306798</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8435,12 +8073,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8455,53 +8093,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119558993</v>
+        <v>113627234</v>
       </c>
       <c r="B78" t="n">
-        <v>90916</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8511,13 +8140,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>762977</v>
+        <v>763248</v>
       </c>
       <c r="R78" t="n">
-        <v>7306896</v>
+        <v>7306836</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8541,12 +8170,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8561,53 +8190,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119559020</v>
+        <v>113627235</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8617,13 +8237,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>763292</v>
+        <v>763277</v>
       </c>
       <c r="R79" t="n">
-        <v>7306865</v>
+        <v>7306835</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8647,12 +8267,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8667,53 +8287,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119557854</v>
+        <v>113627236</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8723,13 +8334,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>762984</v>
+        <v>763325</v>
       </c>
       <c r="R80" t="n">
-        <v>7306966</v>
+        <v>7306890</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8753,12 +8364,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8773,31 +8384,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119558862</v>
+        <v>113627237</v>
       </c>
       <c r="B81" t="n">
-        <v>95455</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8805,21 +8407,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8829,13 +8431,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>763006</v>
+        <v>763371</v>
       </c>
       <c r="R81" t="n">
-        <v>7306911</v>
+        <v>7306912</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8859,12 +8461,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8879,53 +8481,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119559023</v>
+        <v>113627238</v>
       </c>
       <c r="B82" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8935,13 +8528,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>762960</v>
+        <v>763385</v>
       </c>
       <c r="R82" t="n">
-        <v>7306894</v>
+        <v>7306919</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8965,12 +8558,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8985,31 +8578,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119558963</v>
+        <v>113627239</v>
       </c>
       <c r="B83" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9017,21 +8601,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9041,13 +8625,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>763032</v>
+        <v>763382</v>
       </c>
       <c r="R83" t="n">
-        <v>7306907</v>
+        <v>7306989</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9071,12 +8655,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9091,53 +8675,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119559016</v>
+        <v>113627243</v>
       </c>
       <c r="B84" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9147,13 +8722,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>763454</v>
+        <v>763506</v>
       </c>
       <c r="R84" t="n">
-        <v>7306636</v>
+        <v>7306778</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9177,12 +8752,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9197,53 +8772,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119558962</v>
+        <v>119557853</v>
       </c>
       <c r="B85" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9253,10 +8819,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>763168</v>
+        <v>763442</v>
       </c>
       <c r="R85" t="n">
-        <v>7306914</v>
+        <v>7306600</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9303,12 +8869,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9319,37 +8885,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119558989</v>
+        <v>119557854</v>
       </c>
       <c r="B86" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9359,10 +8920,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>763410</v>
+        <v>762984</v>
       </c>
       <c r="R86" t="n">
-        <v>7306680</v>
+        <v>7306966</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9409,12 +8970,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9425,37 +8986,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119557869</v>
+        <v>119557856</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9465,10 +9021,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>763366</v>
+        <v>762996</v>
       </c>
       <c r="R87" t="n">
-        <v>7306697</v>
+        <v>7306937</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9531,37 +9087,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119558957</v>
+        <v>119559016</v>
       </c>
       <c r="B88" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9571,10 +9122,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>763026</v>
+        <v>763454</v>
       </c>
       <c r="R88" t="n">
-        <v>7306885</v>
+        <v>7306636</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9637,37 +9188,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119558863</v>
+        <v>119559017</v>
       </c>
       <c r="B89" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9677,10 +9223,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>762972</v>
+        <v>763421</v>
       </c>
       <c r="R89" t="n">
-        <v>7306899</v>
+        <v>7306683</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9727,12 +9273,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9743,15 +9289,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119559024</v>
+        <v>119559018</v>
       </c>
       <c r="B90" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9783,10 +9324,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>762953</v>
+        <v>763383</v>
       </c>
       <c r="R90" t="n">
-        <v>7306896</v>
+        <v>7306714</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9849,15 +9390,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119695058</v>
+        <v>119559019</v>
       </c>
       <c r="B91" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9885,14 +9421,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>S Fällfors, Nb</t>
+          <t>Fällforsen, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>763283</v>
+        <v>763302</v>
       </c>
       <c r="R91" t="n">
-        <v>7306863</v>
+        <v>7306822</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9939,62 +9475,61 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119695069</v>
+        <v>119559020</v>
       </c>
       <c r="B92" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>S Fällfors, Nb</t>
+          <t>Fällforsen, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>763016</v>
+        <v>763292</v>
       </c>
       <c r="R92" t="n">
-        <v>7306889</v>
+        <v>7306865</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10041,27 +9576,26 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119695059</v>
+        <v>119559021</v>
       </c>
       <c r="B93" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10089,14 +9623,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>S Fällfors, Nb</t>
+          <t>Fällforsen, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>763192</v>
+        <v>763222</v>
       </c>
       <c r="R93" t="n">
-        <v>7306872</v>
+        <v>7306894</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10143,62 +9677,61 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119695005</v>
+        <v>119559022</v>
       </c>
       <c r="B94" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>S Fällfors, Nb</t>
+          <t>Fällforsen, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>763016</v>
+        <v>763106</v>
       </c>
       <c r="R94" t="n">
-        <v>7306911</v>
+        <v>7306889</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10245,27 +9778,26 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119695064</v>
+        <v>119559023</v>
       </c>
       <c r="B95" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10293,14 +9825,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>S Fällfors, Nb</t>
+          <t>Fällforsen, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>763050</v>
+        <v>762960</v>
       </c>
       <c r="R95" t="n">
-        <v>7306886</v>
+        <v>7306894</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10347,62 +9879,61 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119695010</v>
+        <v>119559024</v>
       </c>
       <c r="B96" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>S Fällfors, Nb</t>
+          <t>Fällforsen, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>763167</v>
+        <v>762953</v>
       </c>
       <c r="R96" t="n">
-        <v>7306873</v>
+        <v>7306896</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10449,27 +9980,26 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119695066</v>
+        <v>119695055</v>
       </c>
       <c r="B97" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10501,10 +10031,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>762938</v>
+        <v>763391</v>
       </c>
       <c r="R97" t="n">
-        <v>7306914</v>
+        <v>7306668</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10563,15 +10093,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119695061</v>
+        <v>119695056</v>
       </c>
       <c r="B98" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10603,10 +10128,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>763114</v>
+        <v>763369</v>
       </c>
       <c r="R98" t="n">
-        <v>7306900</v>
+        <v>7306687</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10665,15 +10190,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119695056</v>
+        <v>119695057</v>
       </c>
       <c r="B99" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10705,10 +10225,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>763369</v>
+        <v>763357</v>
       </c>
       <c r="R99" t="n">
-        <v>7306687</v>
+        <v>7306688</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10767,37 +10287,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119695009</v>
+        <v>119695058</v>
       </c>
       <c r="B100" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10807,10 +10322,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>763345</v>
+        <v>763283</v>
       </c>
       <c r="R100" t="n">
-        <v>7306702</v>
+        <v>7306863</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10869,15 +10384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119695065</v>
+        <v>119695059</v>
       </c>
       <c r="B101" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10909,10 +10419,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>762943</v>
+        <v>763192</v>
       </c>
       <c r="R101" t="n">
-        <v>7306899</v>
+        <v>7306872</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10971,15 +10481,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119695063</v>
+        <v>119695060</v>
       </c>
       <c r="B102" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11011,10 +10516,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>763054</v>
+        <v>763155</v>
       </c>
       <c r="R102" t="n">
-        <v>7306878</v>
+        <v>7306883</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11073,15 +10578,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119695060</v>
+        <v>119695061</v>
       </c>
       <c r="B103" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11113,10 +10613,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>763155</v>
+        <v>763114</v>
       </c>
       <c r="R103" t="n">
-        <v>7306883</v>
+        <v>7306900</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11178,12 +10678,7 @@
         <v>119695062</v>
       </c>
       <c r="B104" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11277,37 +10772,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119695004</v>
+        <v>119695063</v>
       </c>
       <c r="B105" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11317,10 +10807,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>763110</v>
+        <v>763054</v>
       </c>
       <c r="R105" t="n">
-        <v>7306907</v>
+        <v>7306878</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11379,15 +10869,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119695057</v>
+        <v>119695064</v>
       </c>
       <c r="B106" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11419,10 +10904,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>763357</v>
+        <v>763050</v>
       </c>
       <c r="R106" t="n">
-        <v>7306688</v>
+        <v>7306886</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11481,15 +10966,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119695055</v>
+        <v>119695065</v>
       </c>
       <c r="B107" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11521,10 +11001,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>763391</v>
+        <v>762943</v>
       </c>
       <c r="R107" t="n">
-        <v>7306668</v>
+        <v>7306899</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11583,45 +11063,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130828516</v>
+        <v>119695066</v>
       </c>
       <c r="B108" t="n">
-        <v>92539</v>
+        <v>99118</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>757</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fällforsen, Nb</t>
+          <t>S Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>763330</v>
+        <v>762938</v>
       </c>
       <c r="R108" t="n">
-        <v>7306842</v>
+        <v>7306914</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11648,12 +11128,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11662,24 +11142,18 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 52981-2023 artfynd.xlsx
+++ b/artfynd/A 52981-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AZ108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558862</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558967</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477173</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477176</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477185</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477187</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477188</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477214</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477222</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477234</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558989</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130828516</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2052,6 +2122,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559029</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2149,6 +2224,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477177</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2246,6 +2326,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477195</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2343,6 +2428,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477209</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2440,6 +2530,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477221</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2537,6 +2632,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477223</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2634,6 +2734,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477231</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2731,6 +2836,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477232</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2828,6 +2938,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477233</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2925,6 +3040,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477254</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3022,6 +3142,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627223</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3123,6 +3248,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558863</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3224,6 +3354,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558962</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3325,6 +3460,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558963</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3422,6 +3562,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477217</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3523,6 +3668,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558993</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3624,6 +3774,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119557792</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3725,6 +3880,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558957</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3822,6 +3982,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695004</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3919,6 +4084,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695005</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4016,6 +4186,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477204</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4113,6 +4288,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477242</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4210,6 +4390,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627257</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4307,6 +4492,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627258</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4404,6 +4594,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627259</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4501,6 +4696,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627260</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4598,6 +4798,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627261</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4695,6 +4900,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627262</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4792,6 +5002,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627263</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4889,6 +5104,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627264</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4986,6 +5206,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627265</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5083,6 +5308,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627266</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5184,6 +5414,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119557869</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5285,6 +5520,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559028</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5382,6 +5622,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695069</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5479,6 +5724,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477247</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5576,6 +5826,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477189</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5673,6 +5928,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477225</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5770,6 +6030,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627252</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5867,6 +6132,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627241</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5964,6 +6234,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627242</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6065,6 +6340,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119557806</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6162,6 +6442,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695009</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6259,6 +6544,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695010</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6356,6 +6646,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477174</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6453,6 +6748,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477180</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6550,6 +6850,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627244</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6647,6 +6952,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627245</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6744,6 +7054,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627246</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6841,6 +7156,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627270</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6938,6 +7258,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477186</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7035,6 +7360,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477194</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7132,6 +7462,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113477237</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7229,6 +7564,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627224</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7326,6 +7666,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627225</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7423,6 +7768,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627226</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7520,6 +7870,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627227</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7617,6 +7972,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627228</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7714,6 +8074,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627229</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7811,6 +8176,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627230</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7908,6 +8278,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627231</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8005,6 +8380,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627232</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8102,6 +8482,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627233</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8199,6 +8584,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627234</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8296,6 +8686,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627235</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8393,6 +8788,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627236</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8490,6 +8890,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627237</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8587,6 +8992,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627238</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8684,6 +9094,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627239</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8781,6 +9196,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113627243</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8882,6 +9302,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119557853</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8983,6 +9408,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119557854</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9084,6 +9514,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119557856</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9185,6 +9620,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559016</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9286,6 +9726,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559017</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9387,6 +9832,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559018</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9488,6 +9938,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559019</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9589,6 +10044,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559020</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9690,6 +10150,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559021</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9791,6 +10256,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559022</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9892,6 +10362,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559023</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9993,6 +10468,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559024</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10090,6 +10570,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695055</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10187,6 +10672,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695056</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10284,6 +10774,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695057</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10381,6 +10876,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695058</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10478,6 +10978,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695059</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10575,6 +11080,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695060</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10672,6 +11182,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695061</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10769,6 +11284,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695062</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10866,6 +11386,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695063</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10963,6 +11488,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695064</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11060,6 +11590,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695065</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11157,8 +11692,122 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119695066</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>